--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19878,7 +19878,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28524,7 +28524,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29310,7 +29310,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30882,7 +30882,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31668,7 +31668,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32454,7 +32454,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33240,7 +33240,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34026,7 +34026,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34812,7 +34812,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35598,7 +35598,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36384,7 +36384,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37170,7 +37170,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37956,7 +37956,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38742,7 +38742,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41100,7 +41100,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41886,7 +41886,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42672,7 +42672,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43458,7 +43458,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44244,7 +44244,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45030,7 +45030,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45816,7 +45816,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46602,7 +46602,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47388,7 +47388,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48174,7 +48174,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48960,7 +48960,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49746,7 +49746,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -50532,7 +50532,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51318,7 +51318,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -52104,7 +52104,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52890,7 +52890,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53676,7 +53676,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54462,7 +54462,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -55248,7 +55248,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -56034,7 +56034,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -56820,7 +56820,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN287" t="b">

--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25370,7 +25370,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34016,7 +34016,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35588,7 +35588,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39518,7 +39518,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40304,7 +40304,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41090,7 +41090,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41876,7 +41876,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42662,7 +42662,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44234,7 +44234,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46592,7 +46592,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47378,7 +47378,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48164,7 +48164,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48950,7 +48950,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -50522,7 +50522,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -51308,7 +51308,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52094,7 +52094,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -53666,7 +53666,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -54452,7 +54452,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55238,7 +55238,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -56024,7 +56024,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56810,7 +56810,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
